--- a/submission/HD-FY2026Q2.xlsx
+++ b/submission/HD-FY2026Q2.xlsx
@@ -1,166 +1,93 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/devansh/hackathonProjects/agents-vs-wall-street/submission/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09AF740B-A780-BB4D-A256-534EB544CDEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
-  <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="34560" windowHeight="20500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-  </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" r:id="rId1"/>
-    <sheet name="Instructions" sheetId="2" r:id="rId2"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="25">
-  <si>
-    <t>Metric</t>
-  </si>
-  <si>
-    <t>Units</t>
-  </si>
-  <si>
-    <t>FY2026Q2</t>
-  </si>
-  <si>
-    <t>Net sales</t>
-  </si>
-  <si>
-    <t>USDm</t>
-  </si>
-  <si>
-    <t>Adjusted diluted EPS</t>
-  </si>
-  <si>
-    <t>USD / share</t>
-  </si>
-  <si>
-    <t>Comparable sales, total company</t>
-  </si>
-  <si>
-    <t>%</t>
-  </si>
-  <si>
-    <t>How to use this workbook</t>
-  </si>
-  <si>
-    <t>Home Depot  •  HD  •  FY2026Q2</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>Make a copy of the supplied template for your final output.</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>On the Summary sheet, fill only the three yellow cells in the period column.</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>Enter numbers, not formulas, text, currency symbols or percent signs.</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>For a percentage row, enter percentage points: 4.5 means 4.5%.</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>For EPS, enter dollars per share: 3.25 means $3.25 per share.</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>Do not rename the Summary sheet, metric labels, units, period header or output file.</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>Save the completed file as HD-FY2026Q2.xlsx in the submission folder.</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
-    <numFmt numFmtId="164" formatCode="#,##0.0;[Red]\(#,##0.0\);\-"/>
-    <numFmt numFmtId="165" formatCode="0.00;[Red]\(0.00\);\-"/>
-    <numFmt numFmtId="166" formatCode="0.0;[Red]\(0.0\);\-"/>
+    <numFmt numFmtId="164" formatCode="#,##0.0;[Red](#,##0.0);-"/>
+    <numFmt numFmtId="165" formatCode="0.00;[Red](0.00);-"/>
+    <numFmt numFmtId="166" formatCode="0.0;[Red](0.0);-"/>
   </numFmts>
-  <fonts count="9">
-    <font>
+  <fonts count="12">
+    <font>
+      <name val="Carlito"/>
       <sz val="11"/>
-      <name val="Carlito"/>
-    </font>
-    <font>
-      <b/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="22"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <color rgb="FFD0D5DD"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos Display"/>
+      <b val="1"/>
+      <color rgb="FF101828"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="FF101828"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF101828"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <color rgb="FF667085"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Aptos"/>
+      <b val="1"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+    </font>
+    <font>
       <name val="Aptos Display"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color rgb="FF155EEF"/>
       <sz val="10"/>
-      <color rgb="FFD0D5DD"/>
+    </font>
+    <font>
       <name val="Aptos Display"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF667085"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <name val="Aptos"/>
-    </font>
-    <font>
+      <b val="1"/>
+      <color rgb="FF155EEF"/>
       <sz val="11"/>
-      <color rgb="FF101828"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF101828"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF667085"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Aptos"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF155EEF"/>
-      <name val="Aptos"/>
     </font>
   </fonts>
   <fills count="7">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -191,13 +118,37 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="9">
+    <border/>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
+      <left style="thin">
+        <color rgb="FFFEC84B"/>
+      </left>
+      <top style="thin">
+        <color rgb="FFFEC84B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFEC84B"/>
+      </bottom>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFFEC84B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFEC84B"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFFEC84B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFEC84B"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFEC84B"/>
+      </bottom>
     </border>
     <border>
       <left style="thin">
@@ -212,7 +163,6 @@
       <bottom style="thin">
         <color rgb="FF155EEF"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -227,7 +177,6 @@
       <bottom style="thin">
         <color rgb="FFD0D5DD"/>
       </bottom>
-      <diagonal/>
     </border>
     <border>
       <left style="thin">
@@ -242,62 +191,234 @@
       <bottom style="thin">
         <color rgb="FFFEC84B"/>
       </bottom>
-      <diagonal/>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="FFFEC84B"/>
+      </top>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="FFFEC84B"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFEC84B"/>
+      </top>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="57">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="7" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -489,149 +610,245 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="48" customWidth="1"/>
-    <col min="2" max="3" width="18" customWidth="1"/>
+    <col width="48" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="25" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
+    <row r="1" ht="34" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Home Depot forecast</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>HD  •  FY2026Q2  •  Agents vs Wall Street</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="38" customHeight="1">
+      <c r="A4" s="51" t="inlineStr">
+        <is>
+          <t>Enter forecasts only in the yellow cells. Keep this sheet name, the metric labels, units and period unchanged.</t>
+        </is>
+      </c>
+      <c r="B4" s="52" t="n"/>
+      <c r="C4" s="53" t="n"/>
+    </row>
+    <row r="6" ht="25" customHeight="1">
+      <c r="A6" s="22" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B6" s="22" t="inlineStr">
+        <is>
+          <t>Units</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>FY2026Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="29" customHeight="1">
+      <c r="A7" s="28" t="inlineStr">
+        <is>
+          <t>Net sales</t>
+        </is>
+      </c>
+      <c r="B7" s="29" t="inlineStr">
+        <is>
+          <t>USDm</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="n">
+        <v>47613</v>
+      </c>
+    </row>
+    <row r="8" ht="29" customHeight="1">
+      <c r="A8" s="28" t="inlineStr">
+        <is>
+          <t>Adjusted diluted EPS</t>
+        </is>
+      </c>
+      <c r="B8" s="29" t="inlineStr">
+        <is>
+          <t>USD / share</t>
+        </is>
+      </c>
+      <c r="C8" s="55" t="n">
+        <v>4.68</v>
+      </c>
+    </row>
+    <row r="9" ht="29" customHeight="1">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>Comparable sales, total company</t>
+        </is>
+      </c>
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="C9" s="56" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="29" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="5">
-        <v>47613</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="29" customHeight="1">
-      <c r="A3" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="6">
-        <v>4.68</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" ht="29" customHeight="1">
-      <c r="A4" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="7">
-        <v>1</v>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="41" t="inlineStr">
+        <is>
+          <t>Before upload: complete entry.json, then run npm run check:submission from the repository root.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="45" t="inlineStr">
+        <is>
+          <t>Percentage rows use percentage points: enter 4.5 for 4.5%. EPS is entered in dollars per share.</t>
+        </is>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A11:C11"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A12:C12"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:D10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="76" customWidth="1"/>
-    <col min="3" max="4" width="4" customWidth="1"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="76" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="4" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="36" customHeight="1">
-      <c r="A1" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="B1" s="10"/>
-      <c r="C1" s="10"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" ht="22" customHeight="1">
-      <c r="A2" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-    </row>
-    <row r="4" spans="1:4" ht="34" customHeight="1">
-      <c r="A4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="34" customHeight="1">
-      <c r="A5" s="9" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="34" customHeight="1">
-      <c r="A6" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="34" customHeight="1">
-      <c r="A7" s="9" t="s">
-        <v>17</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" ht="34" customHeight="1">
-      <c r="A8" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="34" customHeight="1">
-      <c r="A9" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="34" customHeight="1">
-      <c r="A10" s="9" t="s">
-        <v>23</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>24</v>
+    <row r="1" ht="36" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>How to use this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="9" t="inlineStr">
+        <is>
+          <t>Home Depot  •  HD  •  FY2026Q2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="34" customHeight="1">
+      <c r="A4" s="50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="47" t="inlineStr">
+        <is>
+          <t>Make a copy of the supplied template for your final output.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="34" customHeight="1">
+      <c r="A5" s="50" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="47" t="inlineStr">
+        <is>
+          <t>On the Summary sheet, fill only the three yellow cells in the period column.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="34" customHeight="1">
+      <c r="A6" s="50" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="47" t="inlineStr">
+        <is>
+          <t>Enter numbers, not formulas, text, currency symbols or percent signs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="34" customHeight="1">
+      <c r="A7" s="50" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>For a percentage row, enter percentage points: 4.5 means 4.5%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" s="50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="47" t="inlineStr">
+        <is>
+          <t>For EPS, enter dollars per share: 3.25 means $3.25 per share.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="34" customHeight="1">
+      <c r="A9" s="50" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="47" t="inlineStr">
+        <is>
+          <t>Do not rename the Summary sheet, metric labels, units, period header or output file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="34" customHeight="1">
+      <c r="A10" s="50" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="47" t="inlineStr">
+        <is>
+          <t>Save the completed file as HD-FY2026Q2.xlsx in the submission folder.</t>
+        </is>
       </c>
     </row>
   </sheetData>
